--- a/data_spek.xlsx
+++ b/data_spek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lian Bhara\Downloads\Project MAP Lian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFF2F4A-C840-4B49-AEBF-8976B2C45C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD79060-0C2F-4D78-81EA-50AE05AFEC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B9A2A030-9CBB-4C37-9F8A-F6C29C0BD6A1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>Lawan_Dicari</t>
   </si>
@@ -92,6 +92,21 @@
   </si>
   <si>
     <t>Kak, S25 emang bagus, tapi nanggung banget! Kalau budget Kakak masuk, saya sangat sarankan langsung ambil S26. S26 ini bawa fitur Galaxy AI generasi paling baru yang jauh lebih pintar buat ngedit foto atau terjemahin bahasa. Layarnya juga jauh lebih terang kalau dipakai di luar ruangan. Plus, karena ini seri paling baru, umur pakainya (update software-nya) dijamin lebih panjang, jadi hitungannya Kakak malah lebih hemat untuk investasi jangka panjang!</t>
+  </si>
+  <si>
+    <t>Poco X8</t>
+  </si>
+  <si>
+    <t>Redmi Note 17 Pro</t>
+  </si>
+  <si>
+    <t>Kak, mending langsung Redmi Note 17 Pro. Spek jeroannya kembar identik dengan Poco X8: prosesor, memori, sampai baterai raksasanya sama persis. Keunggulannya, bodi Redmi Note jauh lebih elegan dan berkelas. Performa gaming tetap rata kanan.</t>
+  </si>
+  <si>
+    <t>✅ Performa Identik: Snapdragon 6s Gen 4 &amp; RAM 6-12GB (Gaming 100% sama).
+✅ Daya Kembar: Baterai 8340mAh + Fast Charging 67W.
+✅ Layar &amp; Kamera Sama: Layar 6.83" (1280x2772) &amp; Kamera Utama 50MP.
+🌟 Nilai Plus Redmi: Desain bodi dan material jauh lebih mewah &amp; premium.</t>
   </si>
 </sst>
 </file>
@@ -466,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865078EF-1A17-4CFF-A56F-F1036E6638B8}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -544,7 +559,22 @@
         <v>14</v>
       </c>
     </row>
+    <row r="6" spans="1:4" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>